--- a/journal.xlsx
+++ b/journal.xlsx
@@ -589,10 +589,10 @@
         <v>0.681</v>
       </c>
       <c r="L3" t="n">
-        <v>2451.2</v>
+        <v>2470.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.045764</v>
+        <v>0.037607</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -639,13 +639,13 @@
         <v>0.118644</v>
       </c>
       <c r="K4" t="n">
-        <v>291.97</v>
+        <v>292.67</v>
       </c>
       <c r="L4" t="n">
-        <v>2451.2</v>
+        <v>2470.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003954</v>
+        <v>-0.001489</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
